--- a/artfynd/A 43981-2023 artfynd.xlsx
+++ b/artfynd/A 43981-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 43981-2023 artfynd.xlsx
+++ b/artfynd/A 43981-2023 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>65011469</v>
       </c>
       <c r="B2" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>511936.9128661481</v>
+        <v>511937</v>
       </c>
       <c r="R2" t="n">
-        <v>7018476.569854693</v>
+        <v>7018477</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,19 +743,9 @@
           <t>2016-09-13</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2016-09-13</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,12 +779,7 @@
         <v>65011467</v>
       </c>
       <c r="B3" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -831,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>511894.5267869529</v>
+        <v>511895</v>
       </c>
       <c r="R3" t="n">
-        <v>7018489.007571878</v>
+        <v>7018489</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -864,19 +844,9 @@
           <t>2016-09-13</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2016-09-13</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -910,12 +880,7 @@
         <v>65011468</v>
       </c>
       <c r="B4" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -947,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>511910.4519724246</v>
+        <v>511910</v>
       </c>
       <c r="R4" t="n">
-        <v>7018567.332912552</v>
+        <v>7018567</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -980,19 +945,9 @@
           <t>2016-09-13</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2016-09-13</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 43981-2023 artfynd.xlsx
+++ b/artfynd/A 43981-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/65011469</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/65011467</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,8 +990,18 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/65011468</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>